--- a/output/SPX_daily_20260720.xlsx
+++ b/output/SPX_daily_20260720.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="14">
+  <fonts count="16">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -79,8 +79,17 @@
     <font>
       <color rgb="00444444"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <color rgb="00333333"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -115,6 +124,16 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00E6EEFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F4E78"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EAF2F8"/>
       </patternFill>
     </fill>
   </fills>
@@ -185,7 +204,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -234,6 +253,9 @@
     <xf numFmtId="0" fontId="12" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -264,6 +286,15 @@
     </xf>
     <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -630,7 +661,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J51"/>
+  <dimension ref="A1:K57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -643,6 +674,7 @@
     <col width="9" customWidth="1" min="8" max="8"/>
     <col width="9" customWidth="1" min="9" max="9"/>
     <col width="26" customWidth="1" min="10" max="10"/>
+    <col width="62" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1" ht="16" customHeight="1">
@@ -768,7 +800,7 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>-0.7</t>
+          <t>-0.6</t>
         </is>
       </c>
       <c r="G6" s="6" t="inlineStr">
@@ -777,7 +809,7 @@
         </is>
       </c>
       <c r="I6" s="6" t="n">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="7">
@@ -797,7 +829,7 @@
         </is>
       </c>
       <c r="I7" s="7" t="n">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="9">
@@ -832,6 +864,11 @@
       <c r="J9" s="8" t="inlineStr">
         <is>
           <t>섹터</t>
+        </is>
+      </c>
+      <c r="K9" s="8" t="inlineStr">
+        <is>
+          <t>주요 사업 요약</t>
         </is>
       </c>
     </row>
@@ -861,8 +898,9 @@
       </c>
       <c r="I10" s="9" t="n"/>
       <c r="J10" s="9" t="n"/>
-    </row>
-    <row r="11" ht="14" customHeight="1">
+      <c r="K10" s="9" t="n"/>
+    </row>
+    <row r="11" ht="28" customHeight="1">
       <c r="A11" s="10" t="n">
         <v>1</v>
       </c>
@@ -907,8 +945,13 @@
           <t>Financials</t>
         </is>
       </c>
-    </row>
-    <row r="12" ht="14" customHeight="1">
+      <c r="K11" s="18" t="inlineStr">
+        <is>
+          <t>Global Payments Inc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="28" customHeight="1">
       <c r="A12" s="10" t="n">
         <v>2</v>
       </c>
@@ -930,12 +973,12 @@
           <t>+4.5</t>
         </is>
       </c>
-      <c r="F12" s="18" t="inlineStr">
+      <c r="F12" s="19" t="inlineStr">
         <is>
           <t>-0.3</t>
         </is>
       </c>
-      <c r="G12" s="18" t="inlineStr">
+      <c r="G12" s="19" t="inlineStr">
         <is>
           <t>-12.0</t>
         </is>
@@ -953,8 +996,13 @@
           <t>Information Technology</t>
         </is>
       </c>
-    </row>
-    <row r="13" ht="14" customHeight="1">
+      <c r="K12" s="18" t="inlineStr">
+        <is>
+          <t>Lumentum Holdings Inc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="28" customHeight="1">
       <c r="A13" s="10" t="n">
         <v>3</v>
       </c>
@@ -976,12 +1024,12 @@
           <t>+3.5</t>
         </is>
       </c>
-      <c r="F13" s="18" t="inlineStr">
+      <c r="F13" s="19" t="inlineStr">
         <is>
           <t>-2.2</t>
         </is>
       </c>
-      <c r="G13" s="18" t="inlineStr">
+      <c r="G13" s="19" t="inlineStr">
         <is>
           <t>-18.3</t>
         </is>
@@ -999,8 +1047,13 @@
           <t>Information Technology</t>
         </is>
       </c>
-    </row>
-    <row r="14" ht="14" customHeight="1">
+      <c r="K13" s="18" t="inlineStr">
+        <is>
+          <t>Teradyne, Inc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="28" customHeight="1">
       <c r="A14" s="10" t="n">
         <v>4</v>
       </c>
@@ -1022,7 +1075,7 @@
           <t>+3.4</t>
         </is>
       </c>
-      <c r="F14" s="18" t="inlineStr">
+      <c r="F14" s="19" t="inlineStr">
         <is>
           <t>-3.6</t>
         </is>
@@ -1045,8 +1098,13 @@
           <t>Industrials</t>
         </is>
       </c>
-    </row>
-    <row r="15" ht="14" customHeight="1">
+      <c r="K14" s="18" t="inlineStr">
+        <is>
+          <t>Axon Enterprise, Inc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="28" customHeight="1">
       <c r="A15" s="10" t="n">
         <v>5</v>
       </c>
@@ -1068,12 +1126,12 @@
           <t>+3.3</t>
         </is>
       </c>
-      <c r="F15" s="18" t="inlineStr">
+      <c r="F15" s="19" t="inlineStr">
         <is>
           <t>-10.4</t>
         </is>
       </c>
-      <c r="G15" s="18" t="inlineStr">
+      <c r="G15" s="19" t="inlineStr">
         <is>
           <t>-32.7</t>
         </is>
@@ -1091,8 +1149,13 @@
           <t>Information Technology</t>
         </is>
       </c>
-    </row>
-    <row r="16" ht="14" customHeight="1">
+      <c r="K15" s="18" t="inlineStr">
+        <is>
+          <t>Marvell Technology, Inc., together with its subsidiaries, provides data infrastructure semiconductor solutions and spanning the data center core to network edge in the United St...</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="28" customHeight="1">
       <c r="A16" s="10" t="n">
         <v>6</v>
       </c>
@@ -1137,8 +1200,13 @@
           <t>Consumer Staples</t>
         </is>
       </c>
-    </row>
-    <row r="17" ht="14" customHeight="1">
+      <c r="K16" s="18" t="inlineStr">
+        <is>
+          <t>Brown-Forman Corporation, together with its subsidiaries, manufactures, distills, bottles, imports, exports, markets, and sells a variety of alcohol beverages.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="28" customHeight="1">
       <c r="A17" s="10" t="n">
         <v>7</v>
       </c>
@@ -1160,12 +1228,12 @@
           <t>+2.8</t>
         </is>
       </c>
-      <c r="F17" s="18" t="inlineStr">
+      <c r="F17" s="19" t="inlineStr">
         <is>
           <t>-7.2</t>
         </is>
       </c>
-      <c r="G17" s="18" t="inlineStr">
+      <c r="G17" s="19" t="inlineStr">
         <is>
           <t>-24.7</t>
         </is>
@@ -1183,8 +1251,13 @@
           <t>Information Technology</t>
         </is>
       </c>
-    </row>
-    <row r="18" ht="14" customHeight="1">
+      <c r="K17" s="18" t="inlineStr">
+        <is>
+          <t>Coherent Corp.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="28" customHeight="1">
       <c r="A18" s="10" t="n">
         <v>8</v>
       </c>
@@ -1206,12 +1279,12 @@
           <t>+2.7</t>
         </is>
       </c>
-      <c r="F18" s="18" t="inlineStr">
+      <c r="F18" s="19" t="inlineStr">
         <is>
           <t>-16.9</t>
         </is>
       </c>
-      <c r="G18" s="18" t="inlineStr">
+      <c r="G18" s="19" t="inlineStr">
         <is>
           <t>-29.0</t>
         </is>
@@ -1229,8 +1302,13 @@
           <t>Information Technology</t>
         </is>
       </c>
-    </row>
-    <row r="19" ht="14" customHeight="1">
+      <c r="K18" s="18" t="inlineStr">
+        <is>
+          <t>Sandisk Corporation develops, manufactures, and sells data storage devices and solutions using NAND flash technology in the United States, Europe, the Middle East, Africa, Asia,...</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="28" customHeight="1">
       <c r="A19" s="10" t="n">
         <v>9</v>
       </c>
@@ -1252,7 +1330,7 @@
           <t>+2.7</t>
         </is>
       </c>
-      <c r="F19" s="18" t="inlineStr">
+      <c r="F19" s="19" t="inlineStr">
         <is>
           <t>-0.3</t>
         </is>
@@ -1275,8 +1353,13 @@
           <t>Consumer Discretionary</t>
         </is>
       </c>
-    </row>
-    <row r="20" ht="14" customHeight="1">
+      <c r="K19" s="18" t="inlineStr">
+        <is>
+          <t>DoorDash, Inc., together with its subsidiaries, operates a commerce platform that connects merchants, consumers, and dashers in the United States and internationally.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="28" customHeight="1">
       <c r="A20" s="10" t="n">
         <v>10</v>
       </c>
@@ -1303,7 +1386,7 @@
           <t>+4.1</t>
         </is>
       </c>
-      <c r="G20" s="18" t="inlineStr">
+      <c r="G20" s="19" t="inlineStr">
         <is>
           <t>-1.7</t>
         </is>
@@ -1321,8 +1404,13 @@
           <t>Materials</t>
         </is>
       </c>
-    </row>
-    <row r="21" ht="14" customHeight="1">
+      <c r="K20" s="18" t="inlineStr">
+        <is>
+          <t>LyondellBasell Industries N.V.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="28" customHeight="1">
       <c r="A21" s="10" t="n">
         <v>11</v>
       </c>
@@ -1344,12 +1432,12 @@
           <t>+2.4</t>
         </is>
       </c>
-      <c r="F21" s="18" t="inlineStr">
+      <c r="F21" s="19" t="inlineStr">
         <is>
           <t>-10.1</t>
         </is>
       </c>
-      <c r="G21" s="18" t="inlineStr">
+      <c r="G21" s="19" t="inlineStr">
         <is>
           <t>-2.3</t>
         </is>
@@ -1367,8 +1455,13 @@
           <t>Health Care</t>
         </is>
       </c>
-    </row>
-    <row r="22" ht="14" customHeight="1">
+      <c r="K21" s="18" t="inlineStr">
+        <is>
+          <t>Elevance Health, Inc., together with its subsidiaries, operates as a health benefits company in the United States.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="28" customHeight="1">
       <c r="A22" s="10" t="n">
         <v>12</v>
       </c>
@@ -1390,12 +1483,12 @@
           <t>+2.4</t>
         </is>
       </c>
-      <c r="F22" s="18" t="inlineStr">
+      <c r="F22" s="19" t="inlineStr">
         <is>
           <t>-1.6</t>
         </is>
       </c>
-      <c r="G22" s="18" t="inlineStr">
+      <c r="G22" s="19" t="inlineStr">
         <is>
           <t>-3.7</t>
         </is>
@@ -1413,8 +1506,13 @@
           <t>Information Technology</t>
         </is>
       </c>
-    </row>
-    <row r="23" ht="14" customHeight="1">
+      <c r="K22" s="18" t="inlineStr">
+        <is>
+          <t>Akamai Technologies, Inc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="28" customHeight="1">
       <c r="A23" s="10" t="n">
         <v>13</v>
       </c>
@@ -1436,12 +1534,12 @@
           <t>+2.3</t>
         </is>
       </c>
-      <c r="F23" s="18" t="inlineStr">
+      <c r="F23" s="19" t="inlineStr">
         <is>
           <t>-1.1</t>
         </is>
       </c>
-      <c r="G23" s="18" t="inlineStr">
+      <c r="G23" s="19" t="inlineStr">
         <is>
           <t>-11.4</t>
         </is>
@@ -1459,8 +1557,13 @@
           <t>Industrials</t>
         </is>
       </c>
-    </row>
-    <row r="24" ht="14" customHeight="1">
+      <c r="K23" s="18" t="inlineStr">
+        <is>
+          <t>Comfort Systems USA, Inc., together with its subsidiaries, provides mechanical and electrical installation, renovation, maintenance, repair, and replacement services for the mec...</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="28" customHeight="1">
       <c r="A24" s="10" t="n">
         <v>14</v>
       </c>
@@ -1482,12 +1585,12 @@
           <t>+2.2</t>
         </is>
       </c>
-      <c r="F24" s="18" t="inlineStr">
+      <c r="F24" s="19" t="inlineStr">
         <is>
           <t>-13.3</t>
         </is>
       </c>
-      <c r="G24" s="18" t="inlineStr">
+      <c r="G24" s="19" t="inlineStr">
         <is>
           <t>-12.2</t>
         </is>
@@ -1505,8 +1608,13 @@
           <t>Health Care</t>
         </is>
       </c>
-    </row>
-    <row r="25" ht="14" customHeight="1">
+      <c r="K24" s="18" t="inlineStr">
+        <is>
+          <t>Intuitive Surgical, Inc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="28" customHeight="1">
       <c r="A25" s="10" t="n">
         <v>15</v>
       </c>
@@ -1551,8 +1659,13 @@
           <t>Information Technology</t>
         </is>
       </c>
-    </row>
-    <row r="26" ht="14" customHeight="1">
+      <c r="K25" s="18" t="inlineStr">
+        <is>
+          <t>Microsoft Corporation develops and supports software, services, devices, and solutions worldwide.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="28" customHeight="1">
       <c r="A26" s="10" t="n">
         <v>16</v>
       </c>
@@ -1574,12 +1687,12 @@
           <t>+2.1</t>
         </is>
       </c>
-      <c r="F26" s="18" t="inlineStr">
+      <c r="F26" s="19" t="inlineStr">
         <is>
           <t>-12.3</t>
         </is>
       </c>
-      <c r="G26" s="18" t="inlineStr">
+      <c r="G26" s="19" t="inlineStr">
         <is>
           <t>-31.6</t>
         </is>
@@ -1597,8 +1710,13 @@
           <t>Information Technology</t>
         </is>
       </c>
-    </row>
-    <row r="27" ht="14" customHeight="1">
+      <c r="K26" s="18" t="inlineStr">
+        <is>
+          <t>Western Digital Corporation develops, manufactures, and sells data storage devices and solutions based on hard disk drive (HDD) technology in the United States, Asia, Europe, th...</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="28" customHeight="1">
       <c r="A27" s="10" t="n">
         <v>17</v>
       </c>
@@ -1643,8 +1761,13 @@
           <t>Consumer Discretionary</t>
         </is>
       </c>
-    </row>
-    <row r="28" ht="14" customHeight="1">
+      <c r="K27" s="18" t="inlineStr">
+        <is>
+          <t>Domino's Pizza, Inc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="28" customHeight="1">
       <c r="A28" s="10" t="n">
         <v>18</v>
       </c>
@@ -1689,8 +1812,13 @@
           <t>Financials</t>
         </is>
       </c>
-    </row>
-    <row r="29" ht="14" customHeight="1">
+      <c r="K28" s="18" t="inlineStr">
+        <is>
+          <t>Transaction &amp; Payment Processing Services 분야의 미국 상장 기업</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="28" customHeight="1">
       <c r="A29" s="10" t="n">
         <v>19</v>
       </c>
@@ -1712,7 +1840,7 @@
           <t>+2.1</t>
         </is>
       </c>
-      <c r="F29" s="18" t="inlineStr">
+      <c r="F29" s="19" t="inlineStr">
         <is>
           <t>-9.5</t>
         </is>
@@ -1735,8 +1863,13 @@
           <t>Financials</t>
         </is>
       </c>
-    </row>
-    <row r="30" ht="14" customHeight="1">
+      <c r="K29" s="18" t="inlineStr">
+        <is>
+          <t>The Progressive Corporation operates as an insurance company in the United States.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="28" customHeight="1">
       <c r="A30" s="10" t="n">
         <v>20</v>
       </c>
@@ -1763,7 +1896,7 @@
           <t>+1.9</t>
         </is>
       </c>
-      <c r="G30" s="18" t="inlineStr">
+      <c r="G30" s="19" t="inlineStr">
         <is>
           <t>-2.7</t>
         </is>
@@ -1781,941 +1914,1065 @@
           <t>Financials</t>
         </is>
       </c>
+      <c r="K30" s="18" t="inlineStr">
+        <is>
+          <t>Coinbase Global, Inc.</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="4" customHeight="1">
-      <c r="A31" s="19" t="n"/>
-      <c r="B31" s="19" t="n"/>
-      <c r="C31" s="19" t="n"/>
-      <c r="D31" s="19" t="n"/>
-      <c r="E31" s="19" t="n"/>
-      <c r="F31" s="19" t="n"/>
-      <c r="G31" s="19" t="n"/>
-      <c r="H31" s="19" t="n"/>
-      <c r="I31" s="19" t="n"/>
-      <c r="J31" s="19" t="n"/>
-    </row>
-    <row r="32" ht="14" customHeight="1">
-      <c r="A32" s="20" t="n">
+      <c r="A31" s="20" t="n"/>
+      <c r="B31" s="20" t="n"/>
+      <c r="C31" s="20" t="n"/>
+      <c r="D31" s="20" t="n"/>
+      <c r="E31" s="20" t="n"/>
+      <c r="F31" s="20" t="n"/>
+      <c r="G31" s="20" t="n"/>
+      <c r="H31" s="20" t="n"/>
+      <c r="I31" s="20" t="n"/>
+      <c r="J31" s="20" t="n"/>
+      <c r="K31" s="20" t="n"/>
+    </row>
+    <row r="32" ht="28" customHeight="1">
+      <c r="A32" s="21" t="n">
         <v>503</v>
       </c>
-      <c r="B32" s="21" t="inlineStr">
+      <c r="B32" s="22" t="inlineStr">
         <is>
           <t>CVNA</t>
         </is>
       </c>
-      <c r="C32" s="22" t="inlineStr">
+      <c r="C32" s="23" t="inlineStr">
         <is>
           <t>Carvana</t>
         </is>
       </c>
-      <c r="D32" s="23" t="n">
+      <c r="D32" s="24" t="n">
         <v>45.9</v>
       </c>
-      <c r="E32" s="24" t="inlineStr">
+      <c r="E32" s="25" t="inlineStr">
         <is>
           <t>-4.8</t>
         </is>
       </c>
-      <c r="F32" s="24" t="inlineStr">
+      <c r="F32" s="25" t="inlineStr">
         <is>
           <t>-1.3</t>
         </is>
       </c>
-      <c r="G32" s="25" t="inlineStr">
+      <c r="G32" s="26" t="inlineStr">
         <is>
           <t>+2.0</t>
         </is>
       </c>
-      <c r="H32" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I32" s="27" t="n">
+      <c r="H32" s="27" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I32" s="28" t="n">
         <v>248</v>
       </c>
-      <c r="J32" s="28" t="inlineStr">
+      <c r="J32" s="29" t="inlineStr">
         <is>
           <t>Consumer Discretionary</t>
         </is>
       </c>
-    </row>
-    <row r="33" ht="14" customHeight="1">
-      <c r="A33" s="20" t="n">
+      <c r="K32" s="30" t="inlineStr">
+        <is>
+          <t>Carvana Co., together with its subsidiaries, operates an e-commerce platform for buying and selling used cars.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="28" customHeight="1">
+      <c r="A33" s="21" t="n">
         <v>502</v>
       </c>
-      <c r="B33" s="21" t="inlineStr">
+      <c r="B33" s="22" t="inlineStr">
         <is>
           <t>HONA</t>
         </is>
       </c>
-      <c r="C33" s="22" t="inlineStr">
+      <c r="C33" s="23" t="inlineStr">
         <is>
           <t>Honeywell Aerospace</t>
         </is>
       </c>
-      <c r="D33" s="23" t="n">
+      <c r="D33" s="24" t="n">
         <v>64.2</v>
       </c>
-      <c r="E33" s="24" t="inlineStr">
+      <c r="E33" s="25" t="inlineStr">
         <is>
           <t>-4.3</t>
         </is>
       </c>
-      <c r="F33" s="24" t="inlineStr">
+      <c r="F33" s="25" t="inlineStr">
         <is>
           <t>-5.0</t>
         </is>
       </c>
-      <c r="G33" s="24" t="inlineStr">
+      <c r="G33" s="25" t="inlineStr">
         <is>
           <t>-25.0</t>
         </is>
       </c>
-      <c r="H33" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I33" s="27" t="n">
+      <c r="H33" s="27" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I33" s="28" t="n">
         <v>194</v>
       </c>
-      <c r="J33" s="28" t="inlineStr">
+      <c r="J33" s="29" t="inlineStr">
         <is>
           <t>Industrials</t>
         </is>
       </c>
-    </row>
-    <row r="34" ht="14" customHeight="1">
-      <c r="A34" s="20" t="n">
+      <c r="K33" s="30" t="inlineStr">
+        <is>
+          <t>Honeywell Aerospace Inc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="28" customHeight="1">
+      <c r="A34" s="21" t="n">
         <v>501</v>
       </c>
-      <c r="B34" s="21" t="inlineStr">
+      <c r="B34" s="22" t="inlineStr">
         <is>
           <t>ORCL</t>
         </is>
       </c>
-      <c r="C34" s="22" t="inlineStr">
+      <c r="C34" s="23" t="inlineStr">
         <is>
           <t>Oracle Corporation</t>
         </is>
       </c>
-      <c r="D34" s="23" t="n">
+      <c r="D34" s="24" t="n">
         <v>349.6</v>
       </c>
-      <c r="E34" s="24" t="inlineStr">
+      <c r="E34" s="25" t="inlineStr">
         <is>
           <t>-4.0</t>
         </is>
       </c>
-      <c r="F34" s="24" t="inlineStr">
+      <c r="F34" s="25" t="inlineStr">
         <is>
           <t>-7.7</t>
         </is>
       </c>
-      <c r="G34" s="24" t="inlineStr">
+      <c r="G34" s="25" t="inlineStr">
         <is>
           <t>-33.6</t>
         </is>
       </c>
-      <c r="H34" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I34" s="27" t="n">
+      <c r="H34" s="27" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I34" s="28" t="n">
         <v>32</v>
       </c>
-      <c r="J34" s="28" t="inlineStr">
+      <c r="J34" s="29" t="inlineStr">
         <is>
           <t>Information Technology</t>
         </is>
       </c>
-    </row>
-    <row r="35" ht="14" customHeight="1">
-      <c r="A35" s="20" t="n">
+      <c r="K34" s="30" t="inlineStr">
+        <is>
+          <t>Oracle Corporation offers products and services that build, run and support enterprise information technology frameworks worldwide.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="28" customHeight="1">
+      <c r="A35" s="21" t="n">
         <v>499</v>
       </c>
-      <c r="B35" s="21" t="inlineStr">
+      <c r="B35" s="22" t="inlineStr">
         <is>
           <t>KKR</t>
         </is>
       </c>
-      <c r="C35" s="22" t="inlineStr">
+      <c r="C35" s="23" t="inlineStr">
         <is>
           <t>KKR &amp; Co.</t>
         </is>
       </c>
-      <c r="D35" s="23" t="n">
+      <c r="D35" s="24" t="n">
         <v>87.09999999999999</v>
       </c>
-      <c r="E35" s="24" t="inlineStr">
+      <c r="E35" s="25" t="inlineStr">
         <is>
           <t>-3.9</t>
         </is>
       </c>
-      <c r="F35" s="25" t="inlineStr">
+      <c r="F35" s="26" t="inlineStr">
         <is>
           <t>+0.1</t>
         </is>
       </c>
-      <c r="G35" s="24" t="inlineStr">
+      <c r="G35" s="25" t="inlineStr">
         <is>
           <t>-0.2</t>
         </is>
       </c>
-      <c r="H35" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I35" s="27" t="n">
+      <c r="H35" s="27" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I35" s="28" t="n">
         <v>139</v>
       </c>
-      <c r="J35" s="28" t="inlineStr">
+      <c r="J35" s="29" t="inlineStr">
         <is>
           <t>Financials</t>
         </is>
       </c>
-    </row>
-    <row r="36" ht="14" customHeight="1">
-      <c r="A36" s="20" t="n">
+      <c r="K35" s="30" t="inlineStr">
+        <is>
+          <t>KKR &amp; Co.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="28" customHeight="1">
+      <c r="A36" s="21" t="n">
         <v>500</v>
       </c>
-      <c r="B36" s="21" t="inlineStr">
+      <c r="B36" s="22" t="inlineStr">
         <is>
           <t>UPS</t>
         </is>
       </c>
-      <c r="C36" s="22" t="inlineStr">
+      <c r="C36" s="23" t="inlineStr">
         <is>
           <t>United Parcel Service</t>
         </is>
       </c>
-      <c r="D36" s="23" t="n">
+      <c r="D36" s="24" t="n">
         <v>96.2</v>
       </c>
-      <c r="E36" s="24" t="inlineStr">
+      <c r="E36" s="25" t="inlineStr">
         <is>
           <t>-3.9</t>
         </is>
       </c>
-      <c r="F36" s="25" t="inlineStr">
+      <c r="F36" s="26" t="inlineStr">
         <is>
           <t>+0.2</t>
         </is>
       </c>
-      <c r="G36" s="25" t="inlineStr">
+      <c r="G36" s="26" t="inlineStr">
         <is>
           <t>+7.6</t>
         </is>
       </c>
-      <c r="H36" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I36" s="27" t="n">
+      <c r="H36" s="27" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I36" s="28" t="n">
         <v>120</v>
       </c>
-      <c r="J36" s="28" t="inlineStr">
+      <c r="J36" s="29" t="inlineStr">
         <is>
           <t>Industrials</t>
         </is>
       </c>
-    </row>
-    <row r="37" ht="14" customHeight="1">
-      <c r="A37" s="20" t="n">
+      <c r="K36" s="30" t="inlineStr">
+        <is>
+          <t>United Parcel Service, Inc., a package delivery and logistics provider, offers transportation and delivery services.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="28" customHeight="1">
+      <c r="A37" s="21" t="n">
         <v>497</v>
       </c>
-      <c r="B37" s="21" t="inlineStr">
+      <c r="B37" s="22" t="inlineStr">
         <is>
           <t>WBD</t>
         </is>
       </c>
-      <c r="C37" s="22" t="inlineStr">
+      <c r="C37" s="23" t="inlineStr">
         <is>
           <t>Warner Bros. Discovery</t>
         </is>
       </c>
-      <c r="D37" s="23" t="n">
+      <c r="D37" s="24" t="n">
         <v>64.8</v>
       </c>
-      <c r="E37" s="24" t="inlineStr">
+      <c r="E37" s="25" t="inlineStr">
         <is>
           <t>-3.8</t>
         </is>
       </c>
-      <c r="F37" s="24" t="inlineStr">
+      <c r="F37" s="25" t="inlineStr">
         <is>
           <t>-4.5</t>
         </is>
       </c>
-      <c r="G37" s="24" t="inlineStr">
+      <c r="G37" s="25" t="inlineStr">
         <is>
           <t>-1.4</t>
         </is>
       </c>
-      <c r="H37" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I37" s="27" t="n">
+      <c r="H37" s="27" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I37" s="28" t="n">
         <v>191</v>
       </c>
-      <c r="J37" s="28" t="inlineStr">
+      <c r="J37" s="29" t="inlineStr">
         <is>
           <t>Communication Services</t>
         </is>
       </c>
-    </row>
-    <row r="38" ht="14" customHeight="1">
-      <c r="A38" s="20" t="n">
+      <c r="K37" s="30" t="inlineStr">
+        <is>
+          <t>Warner Bros.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="28" customHeight="1">
+      <c r="A38" s="21" t="n">
         <v>498</v>
       </c>
-      <c r="B38" s="21" t="inlineStr">
+      <c r="B38" s="22" t="inlineStr">
         <is>
           <t>CMG</t>
         </is>
       </c>
-      <c r="C38" s="22" t="inlineStr">
+      <c r="C38" s="23" t="inlineStr">
         <is>
           <t>Chipotle Mexican Grill</t>
         </is>
       </c>
-      <c r="D38" s="23" t="n">
+      <c r="D38" s="24" t="n">
         <v>42.5</v>
       </c>
-      <c r="E38" s="24" t="inlineStr">
+      <c r="E38" s="25" t="inlineStr">
         <is>
           <t>-3.8</t>
         </is>
       </c>
-      <c r="F38" s="24" t="inlineStr">
+      <c r="F38" s="25" t="inlineStr">
         <is>
           <t>-9.6</t>
         </is>
       </c>
-      <c r="G38" s="25" t="inlineStr">
+      <c r="G38" s="26" t="inlineStr">
         <is>
           <t>+4.0</t>
         </is>
       </c>
-      <c r="H38" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I38" s="27" t="n">
+      <c r="H38" s="27" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I38" s="28" t="n">
         <v>257</v>
       </c>
-      <c r="J38" s="28" t="inlineStr">
+      <c r="J38" s="29" t="inlineStr">
         <is>
           <t>Consumer Discretionary</t>
         </is>
       </c>
-    </row>
-    <row r="39" ht="14" customHeight="1">
-      <c r="A39" s="20" t="n">
+      <c r="K38" s="30" t="inlineStr">
+        <is>
+          <t>Chipotle Mexican Grill, Inc., together with its subsidiaries, owns and operates Chipotle Mexican Grill restaurants.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="28" customHeight="1">
+      <c r="A39" s="21" t="n">
         <v>496</v>
       </c>
-      <c r="B39" s="21" t="inlineStr">
+      <c r="B39" s="22" t="inlineStr">
         <is>
           <t>MRNA</t>
         </is>
       </c>
-      <c r="C39" s="22" t="inlineStr">
+      <c r="C39" s="23" t="inlineStr">
         <is>
           <t>Moderna</t>
         </is>
       </c>
-      <c r="D39" s="23" t="n">
+      <c r="D39" s="24" t="n">
         <v>23.6</v>
       </c>
-      <c r="E39" s="24" t="inlineStr">
+      <c r="E39" s="25" t="inlineStr">
         <is>
           <t>-3.8</t>
         </is>
       </c>
-      <c r="F39" s="24" t="inlineStr">
+      <c r="F39" s="25" t="inlineStr">
         <is>
           <t>-11.2</t>
         </is>
       </c>
-      <c r="G39" s="24" t="inlineStr">
+      <c r="G39" s="25" t="inlineStr">
         <is>
           <t>-3.7</t>
         </is>
       </c>
-      <c r="H39" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I39" s="27" t="n">
+      <c r="H39" s="27" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I39" s="28" t="n">
         <v>365</v>
       </c>
-      <c r="J39" s="28" t="inlineStr">
+      <c r="J39" s="29" t="inlineStr">
         <is>
           <t>Health Care</t>
         </is>
       </c>
-    </row>
-    <row r="40" ht="14" customHeight="1">
-      <c r="A40" s="20" t="n">
+      <c r="K39" s="30" t="inlineStr">
+        <is>
+          <t>Moderna, Inc., a biotechnology company, provides messenger RNA medicines in the United States, Europe, and internationally.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="28" customHeight="1">
+      <c r="A40" s="21" t="n">
         <v>495</v>
       </c>
-      <c r="B40" s="21" t="inlineStr">
+      <c r="B40" s="22" t="inlineStr">
         <is>
           <t>DELL</t>
         </is>
       </c>
-      <c r="C40" s="22" t="inlineStr">
+      <c r="C40" s="23" t="inlineStr">
         <is>
           <t>Dell Technologies</t>
         </is>
       </c>
-      <c r="D40" s="23" t="n">
+      <c r="D40" s="24" t="n">
         <v>246.7</v>
       </c>
-      <c r="E40" s="24" t="inlineStr">
+      <c r="E40" s="25" t="inlineStr">
         <is>
           <t>-3.6</t>
         </is>
       </c>
-      <c r="F40" s="24" t="inlineStr">
+      <c r="F40" s="25" t="inlineStr">
         <is>
           <t>-10.6</t>
         </is>
       </c>
-      <c r="G40" s="24" t="inlineStr">
+      <c r="G40" s="25" t="inlineStr">
         <is>
           <t>-8.9</t>
         </is>
       </c>
-      <c r="H40" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I40" s="27" t="n">
+      <c r="H40" s="27" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I40" s="28" t="n">
         <v>47</v>
       </c>
-      <c r="J40" s="28" t="inlineStr">
+      <c r="J40" s="29" t="inlineStr">
         <is>
           <t>Information Technology</t>
         </is>
       </c>
-    </row>
-    <row r="41" ht="14" customHeight="1">
-      <c r="A41" s="20" t="n">
+      <c r="K40" s="30" t="inlineStr">
+        <is>
+          <t>Dell Technologies Inc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="28" customHeight="1">
+      <c r="A41" s="21" t="n">
         <v>493</v>
       </c>
-      <c r="B41" s="21" t="inlineStr">
+      <c r="B41" s="22" t="inlineStr">
         <is>
           <t>ARES</t>
         </is>
       </c>
-      <c r="C41" s="22" t="inlineStr">
+      <c r="C41" s="23" t="inlineStr">
         <is>
           <t>Ares Management</t>
         </is>
       </c>
-      <c r="D41" s="23" t="n">
+      <c r="D41" s="24" t="n">
         <v>27.3</v>
       </c>
-      <c r="E41" s="24" t="inlineStr">
+      <c r="E41" s="25" t="inlineStr">
         <is>
           <t>-3.5</t>
         </is>
       </c>
-      <c r="F41" s="25" t="inlineStr">
+      <c r="F41" s="26" t="inlineStr">
         <is>
           <t>+0.7</t>
         </is>
       </c>
-      <c r="G41" s="24" t="inlineStr">
+      <c r="G41" s="25" t="inlineStr">
         <is>
           <t>-5.5</t>
         </is>
       </c>
-      <c r="H41" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I41" s="27" t="n">
+      <c r="H41" s="27" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I41" s="28" t="n">
         <v>339</v>
       </c>
-      <c r="J41" s="28" t="inlineStr">
+      <c r="J41" s="29" t="inlineStr">
         <is>
           <t>Financials</t>
         </is>
       </c>
-    </row>
-    <row r="42" ht="14" customHeight="1">
-      <c r="A42" s="20" t="n">
+      <c r="K41" s="30" t="inlineStr">
+        <is>
+          <t>Ares Management Corporation operates as an alternative asset manager.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="28" customHeight="1">
+      <c r="A42" s="21" t="n">
         <v>494</v>
       </c>
-      <c r="B42" s="21" t="inlineStr">
+      <c r="B42" s="22" t="inlineStr">
         <is>
           <t>IP</t>
         </is>
       </c>
-      <c r="C42" s="22" t="inlineStr">
+      <c r="C42" s="23" t="inlineStr">
         <is>
           <t>International Paper</t>
         </is>
       </c>
-      <c r="D42" s="23" t="n">
+      <c r="D42" s="24" t="n">
         <v>19.2</v>
       </c>
-      <c r="E42" s="24" t="inlineStr">
+      <c r="E42" s="25" t="inlineStr">
         <is>
           <t>-3.5</t>
         </is>
       </c>
-      <c r="F42" s="24" t="inlineStr">
+      <c r="F42" s="25" t="inlineStr">
         <is>
           <t>-2.0</t>
         </is>
       </c>
-      <c r="G42" s="25" t="inlineStr">
+      <c r="G42" s="26" t="inlineStr">
         <is>
           <t>+0.2</t>
         </is>
       </c>
-      <c r="H42" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I42" s="27" t="n">
+      <c r="H42" s="27" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I42" s="28" t="n">
         <v>408</v>
       </c>
-      <c r="J42" s="28" t="inlineStr">
+      <c r="J42" s="29" t="inlineStr">
         <is>
           <t>Materials</t>
         </is>
       </c>
-    </row>
-    <row r="43" ht="14" customHeight="1">
-      <c r="A43" s="20" t="n">
+      <c r="K42" s="30" t="inlineStr">
+        <is>
+          <t>International Paper Company produces and sells renewable fiber-based packaging in North America, Latin America, Europe, South America, and North Africa.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="28" customHeight="1">
+      <c r="A43" s="21" t="n">
         <v>492</v>
       </c>
-      <c r="B43" s="21" t="inlineStr">
+      <c r="B43" s="22" t="inlineStr">
         <is>
           <t>RVTY</t>
         </is>
       </c>
-      <c r="C43" s="22" t="inlineStr">
+      <c r="C43" s="23" t="inlineStr">
         <is>
           <t>Revvity</t>
         </is>
       </c>
-      <c r="D43" s="23" t="n">
+      <c r="D43" s="24" t="n">
         <v>11.9</v>
       </c>
-      <c r="E43" s="24" t="inlineStr">
+      <c r="E43" s="25" t="inlineStr">
         <is>
           <t>-3.4</t>
         </is>
       </c>
-      <c r="F43" s="24" t="inlineStr">
+      <c r="F43" s="25" t="inlineStr">
         <is>
           <t>-4.1</t>
         </is>
       </c>
-      <c r="G43" s="25" t="inlineStr">
+      <c r="G43" s="26" t="inlineStr">
         <is>
           <t>+8.9</t>
         </is>
       </c>
-      <c r="H43" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I43" s="27" t="n">
+      <c r="H43" s="27" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I43" s="28" t="n">
         <v>472</v>
       </c>
-      <c r="J43" s="28" t="inlineStr">
+      <c r="J43" s="29" t="inlineStr">
         <is>
           <t>Health Care</t>
         </is>
       </c>
-    </row>
-    <row r="44" ht="14" customHeight="1">
-      <c r="A44" s="20" t="n">
+      <c r="K43" s="30" t="inlineStr">
+        <is>
+          <t>Revvity, Inc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="28" customHeight="1">
+      <c r="A44" s="21" t="n">
         <v>491</v>
       </c>
-      <c r="B44" s="21" t="inlineStr">
+      <c r="B44" s="22" t="inlineStr">
         <is>
           <t>FSLR</t>
         </is>
       </c>
-      <c r="C44" s="22" t="inlineStr">
+      <c r="C44" s="23" t="inlineStr">
         <is>
           <t>First Solar</t>
         </is>
       </c>
-      <c r="D44" s="23" t="n">
+      <c r="D44" s="24" t="n">
         <v>22.1</v>
       </c>
-      <c r="E44" s="24" t="inlineStr">
+      <c r="E44" s="25" t="inlineStr">
         <is>
           <t>-3.2</t>
         </is>
       </c>
-      <c r="F44" s="24" t="inlineStr">
+      <c r="F44" s="25" t="inlineStr">
         <is>
           <t>-7.1</t>
         </is>
       </c>
-      <c r="G44" s="24" t="inlineStr">
+      <c r="G44" s="25" t="inlineStr">
         <is>
           <t>-19.4</t>
         </is>
       </c>
-      <c r="H44" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I44" s="27" t="n">
+      <c r="H44" s="27" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I44" s="28" t="n">
         <v>386</v>
       </c>
-      <c r="J44" s="28" t="inlineStr">
+      <c r="J44" s="29" t="inlineStr">
         <is>
           <t>Information Technology</t>
         </is>
       </c>
-    </row>
-    <row r="45" ht="14" customHeight="1">
-      <c r="A45" s="20" t="n">
+      <c r="K44" s="30" t="inlineStr">
+        <is>
+          <t>First Solar, Inc., a solar technology company, provides photovoltaic (PV) solar energy solutions in the United States, France, India, Chile, and internationally.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="28" customHeight="1">
+      <c r="A45" s="21" t="n">
         <v>489</v>
       </c>
-      <c r="B45" s="21" t="inlineStr">
+      <c r="B45" s="22" t="inlineStr">
         <is>
           <t>WAT</t>
         </is>
       </c>
-      <c r="C45" s="22" t="inlineStr">
+      <c r="C45" s="23" t="inlineStr">
         <is>
           <t>Waters Corporation</t>
         </is>
       </c>
-      <c r="D45" s="23" t="n">
+      <c r="D45" s="24" t="n">
         <v>35.1</v>
       </c>
-      <c r="E45" s="24" t="inlineStr">
+      <c r="E45" s="25" t="inlineStr">
         <is>
           <t>-3.1</t>
         </is>
       </c>
-      <c r="F45" s="24" t="inlineStr">
+      <c r="F45" s="25" t="inlineStr">
         <is>
           <t>-4.2</t>
         </is>
       </c>
-      <c r="G45" s="25" t="inlineStr">
+      <c r="G45" s="26" t="inlineStr">
         <is>
           <t>+0.2</t>
         </is>
       </c>
-      <c r="H45" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I45" s="27" t="n">
+      <c r="H45" s="27" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I45" s="28" t="n">
         <v>288</v>
       </c>
-      <c r="J45" s="28" t="inlineStr">
+      <c r="J45" s="29" t="inlineStr">
         <is>
           <t>Health Care</t>
         </is>
       </c>
-    </row>
-    <row r="46" ht="14" customHeight="1">
-      <c r="A46" s="20" t="n">
+      <c r="K45" s="30" t="inlineStr">
+        <is>
+          <t>Waters Corporation provides analytical workflow solutions in Asia, the Americas, and Europe.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="28" customHeight="1">
+      <c r="A46" s="21" t="n">
         <v>490</v>
       </c>
-      <c r="B46" s="21" t="inlineStr">
+      <c r="B46" s="22" t="inlineStr">
         <is>
           <t>DHI</t>
         </is>
       </c>
-      <c r="C46" s="22" t="inlineStr">
+      <c r="C46" s="23" t="inlineStr">
         <is>
           <t>D. R. Horton</t>
         </is>
       </c>
-      <c r="D46" s="23" t="n">
+      <c r="D46" s="24" t="n">
         <v>41.1</v>
       </c>
-      <c r="E46" s="24" t="inlineStr">
+      <c r="E46" s="25" t="inlineStr">
         <is>
           <t>-3.1</t>
         </is>
       </c>
-      <c r="F46" s="24" t="inlineStr">
+      <c r="F46" s="25" t="inlineStr">
         <is>
           <t>-2.7</t>
         </is>
       </c>
-      <c r="G46" s="24" t="inlineStr">
+      <c r="G46" s="25" t="inlineStr">
         <is>
           <t>-5.0</t>
         </is>
       </c>
-      <c r="H46" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I46" s="27" t="n">
+      <c r="H46" s="27" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I46" s="28" t="n">
         <v>263</v>
       </c>
-      <c r="J46" s="28" t="inlineStr">
+      <c r="J46" s="29" t="inlineStr">
         <is>
           <t>Consumer Discretionary</t>
         </is>
       </c>
-    </row>
-    <row r="47" ht="14" customHeight="1">
-      <c r="A47" s="20" t="n">
+      <c r="K46" s="30" t="inlineStr">
+        <is>
+          <t>D.R.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="28" customHeight="1">
+      <c r="A47" s="21" t="n">
         <v>488</v>
       </c>
-      <c r="B47" s="21" t="inlineStr">
+      <c r="B47" s="22" t="inlineStr">
         <is>
           <t>URI</t>
         </is>
       </c>
-      <c r="C47" s="22" t="inlineStr">
+      <c r="C47" s="23" t="inlineStr">
         <is>
           <t>United Rentals</t>
         </is>
       </c>
-      <c r="D47" s="23" t="n">
+      <c r="D47" s="24" t="n">
         <v>63.4</v>
       </c>
-      <c r="E47" s="24" t="inlineStr">
+      <c r="E47" s="25" t="inlineStr">
         <is>
           <t>-3.1</t>
         </is>
       </c>
-      <c r="F47" s="24" t="inlineStr">
+      <c r="F47" s="25" t="inlineStr">
         <is>
           <t>-6.7</t>
         </is>
       </c>
-      <c r="G47" s="24" t="inlineStr">
+      <c r="G47" s="25" t="inlineStr">
         <is>
           <t>-3.5</t>
         </is>
       </c>
-      <c r="H47" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I47" s="27" t="n">
+      <c r="H47" s="27" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I47" s="28" t="n">
         <v>195</v>
       </c>
-      <c r="J47" s="28" t="inlineStr">
+      <c r="J47" s="29" t="inlineStr">
         <is>
           <t>Industrials</t>
         </is>
       </c>
-    </row>
-    <row r="48" ht="14" customHeight="1">
-      <c r="A48" s="20" t="n">
+      <c r="K47" s="30" t="inlineStr">
+        <is>
+          <t>United Rentals, Inc., through its subsidiaries, operates as an equipment rental company in the United States, Canada, Europe, Australia, and New Zealand.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="28" customHeight="1">
+      <c r="A48" s="21" t="n">
         <v>485</v>
       </c>
-      <c r="B48" s="21" t="inlineStr">
+      <c r="B48" s="22" t="inlineStr">
         <is>
           <t>SWK</t>
         </is>
       </c>
-      <c r="C48" s="22" t="inlineStr">
+      <c r="C48" s="23" t="inlineStr">
         <is>
           <t>Stanley Black &amp; Decker</t>
         </is>
       </c>
-      <c r="D48" s="23" t="n">
+      <c r="D48" s="24" t="n">
         <v>13.6</v>
       </c>
-      <c r="E48" s="24" t="inlineStr">
+      <c r="E48" s="25" t="inlineStr">
         <is>
           <t>-3.0</t>
         </is>
       </c>
-      <c r="F48" s="25" t="inlineStr">
+      <c r="F48" s="26" t="inlineStr">
         <is>
           <t>+1.1</t>
         </is>
       </c>
-      <c r="G48" s="25" t="inlineStr">
+      <c r="G48" s="26" t="inlineStr">
         <is>
           <t>+6.1</t>
         </is>
       </c>
-      <c r="H48" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I48" s="27" t="n">
+      <c r="H48" s="27" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I48" s="28" t="n">
         <v>454</v>
       </c>
-      <c r="J48" s="28" t="inlineStr">
+      <c r="J48" s="29" t="inlineStr">
         <is>
           <t>Industrials</t>
         </is>
       </c>
-    </row>
-    <row r="49" ht="14" customHeight="1">
-      <c r="A49" s="20" t="n">
+      <c r="K48" s="30" t="inlineStr">
+        <is>
+          <t>Stanley Black &amp; Decker, Inc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="28" customHeight="1">
+      <c r="A49" s="21" t="n">
         <v>486</v>
       </c>
-      <c r="B49" s="21" t="inlineStr">
+      <c r="B49" s="22" t="inlineStr">
         <is>
           <t>TSLA</t>
         </is>
       </c>
-      <c r="C49" s="22" t="inlineStr">
+      <c r="C49" s="23" t="inlineStr">
         <is>
           <t>Tesla, Inc.</t>
         </is>
       </c>
-      <c r="D49" s="23" t="n">
+      <c r="D49" s="24" t="n">
         <v>1388</v>
       </c>
-      <c r="E49" s="24" t="inlineStr">
+      <c r="E49" s="25" t="inlineStr">
         <is>
           <t>-3.0</t>
         </is>
       </c>
-      <c r="F49" s="24" t="inlineStr">
+      <c r="F49" s="25" t="inlineStr">
         <is>
           <t>-6.4</t>
         </is>
       </c>
-      <c r="G49" s="24" t="inlineStr">
+      <c r="G49" s="25" t="inlineStr">
         <is>
           <t>-6.8</t>
         </is>
       </c>
-      <c r="H49" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I49" s="27" t="n">
+      <c r="H49" s="27" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I49" s="28" t="n">
         <v>9</v>
       </c>
-      <c r="J49" s="28" t="inlineStr">
+      <c r="J49" s="29" t="inlineStr">
         <is>
           <t>Consumer Discretionary</t>
         </is>
       </c>
-    </row>
-    <row r="50" ht="14" customHeight="1">
-      <c r="A50" s="20" t="n">
+      <c r="K49" s="30" t="inlineStr">
+        <is>
+          <t>Tesla, Inc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="28" customHeight="1">
+      <c r="A50" s="21" t="n">
         <v>487</v>
       </c>
-      <c r="B50" s="21" t="inlineStr">
+      <c r="B50" s="22" t="inlineStr">
         <is>
           <t>EXPD</t>
         </is>
       </c>
-      <c r="C50" s="22" t="inlineStr">
+      <c r="C50" s="23" t="inlineStr">
         <is>
           <t>Expeditors International</t>
         </is>
       </c>
-      <c r="D50" s="23" t="n">
+      <c r="D50" s="24" t="n">
         <v>23.2</v>
       </c>
-      <c r="E50" s="24" t="inlineStr">
+      <c r="E50" s="25" t="inlineStr">
         <is>
           <t>-3.0</t>
         </is>
       </c>
-      <c r="F50" s="25" t="inlineStr">
+      <c r="F50" s="26" t="inlineStr">
         <is>
           <t>+1.1</t>
         </is>
       </c>
-      <c r="G50" s="25" t="inlineStr">
+      <c r="G50" s="26" t="inlineStr">
         <is>
           <t>+10.4</t>
         </is>
       </c>
-      <c r="H50" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I50" s="27" t="n">
+      <c r="H50" s="27" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I50" s="28" t="n">
         <v>372</v>
       </c>
-      <c r="J50" s="28" t="inlineStr">
+      <c r="J50" s="29" t="inlineStr">
         <is>
           <t>Industrials</t>
         </is>
       </c>
-    </row>
-    <row r="51" ht="14" customHeight="1">
-      <c r="A51" s="20" t="n">
+      <c r="K50" s="30" t="inlineStr">
+        <is>
+          <t>Expeditors International of Washington, Inc., together with its subsidiaries, provides logistics services in the Americas, North Asia, South Asia, Europe, and Middle East, Afric...</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="28" customHeight="1">
+      <c r="A51" s="21" t="n">
         <v>484</v>
       </c>
-      <c r="B51" s="21" t="inlineStr">
+      <c r="B51" s="22" t="inlineStr">
         <is>
           <t>CRH</t>
         </is>
       </c>
-      <c r="C51" s="22" t="inlineStr">
+      <c r="C51" s="23" t="inlineStr">
         <is>
           <t>CRH plc</t>
         </is>
       </c>
-      <c r="D51" s="23" t="n">
+      <c r="D51" s="24" t="n">
         <v>66.8</v>
       </c>
-      <c r="E51" s="24" t="inlineStr">
+      <c r="E51" s="25" t="inlineStr">
         <is>
           <t>-2.9</t>
         </is>
       </c>
-      <c r="F51" s="24" t="inlineStr">
+      <c r="F51" s="25" t="inlineStr">
         <is>
           <t>-2.7</t>
         </is>
       </c>
-      <c r="G51" s="24" t="inlineStr">
+      <c r="G51" s="25" t="inlineStr">
         <is>
           <t>-8.6</t>
         </is>
       </c>
-      <c r="H51" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I51" s="27" t="n">
+      <c r="H51" s="27" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I51" s="28" t="n">
         <v>183</v>
       </c>
-      <c r="J51" s="28" t="inlineStr">
+      <c r="J51" s="29" t="inlineStr">
         <is>
           <t>Materials</t>
         </is>
       </c>
-    </row>
+      <c r="K51" s="30" t="inlineStr">
+        <is>
+          <t>CRH plc, together with its subsidiaries, provides building materials solutions in Ireland, the United States, the United Kingdom, rest of Europe, and internationally.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="31" t="inlineStr">
+        <is>
+          <t>📈 금일 시황 요약 — 하락 종목이 시장 전반으로 확산된 강한 위험회피 흐름</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="58" customHeight="1">
+      <c r="A55" s="32" t="inlineStr">
+        <is>
+          <t>관측: 상승 157개·하락 326개로 상승 비율은 33%였습니다. 강세 섹터는 Communication Services +1.0%, Energy +0.6%, 약세 섹터는 Health Care -1.2%, Materials -0.9%였습니다. 개별 종목 중 GPN(+5.8%)가 가장 강했고, CVNA(-4.8%)가 가장 약했습니다.
+해석: 시장 폭이 약해 단기적으로 방어적 포지셔닝과 변동성 확대 가능성에 유의할 구간입니다.
+유의: 본 요약은 가격·시장 폭·섹터 수익률에 근거한 관측이며, 뉴스·실적 등 원인을 직접 분석한 투자 의견은 아닙니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56"/>
+    <row r="57"/>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="13">
     <mergeCell ref="C9:C10"/>
     <mergeCell ref="B9:B10"/>
     <mergeCell ref="D9:D10"/>
@@ -2724,6 +2981,9 @@
     <mergeCell ref="G7:H7"/>
     <mergeCell ref="A9:A10"/>
     <mergeCell ref="J9:J10"/>
+    <mergeCell ref="K9:K10"/>
+    <mergeCell ref="A54:K54"/>
+    <mergeCell ref="A55:K57"/>
     <mergeCell ref="G2:J5"/>
     <mergeCell ref="G6:H6"/>
   </mergeCells>

--- a/output/SPX_daily_20260720.xlsx
+++ b/output/SPX_daily_20260720.xlsx
@@ -661,7 +661,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K57"/>
+  <dimension ref="A1:L57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -674,7 +674,8 @@
     <col width="9" customWidth="1" min="8" max="8"/>
     <col width="9" customWidth="1" min="9" max="9"/>
     <col width="26" customWidth="1" min="10" max="10"/>
-    <col width="62" customWidth="1" min="11" max="11"/>
+    <col width="46" customWidth="1" min="11" max="11"/>
+    <col width="62" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1" ht="16" customHeight="1">
@@ -869,6 +870,11 @@
       <c r="K9" s="8" t="inlineStr">
         <is>
           <t>주요 사업 요약</t>
+        </is>
+      </c>
+      <c r="L9" s="8" t="inlineStr">
+        <is>
+          <t>등락 이유 (뉴스 근거)</t>
         </is>
       </c>
     </row>
@@ -899,8 +905,9 @@
       <c r="I10" s="9" t="n"/>
       <c r="J10" s="9" t="n"/>
       <c r="K10" s="9" t="n"/>
-    </row>
-    <row r="11" ht="28" customHeight="1">
+      <c r="L10" s="9" t="n"/>
+    </row>
+    <row r="11" ht="42" customHeight="1">
       <c r="A11" s="10" t="n">
         <v>1</v>
       </c>
@@ -950,8 +957,13 @@
           <t>Global Payments Inc.</t>
         </is>
       </c>
-    </row>
-    <row r="12" ht="28" customHeight="1">
+      <c r="L11" s="18" t="inlineStr">
+        <is>
+          <t>당일 뉴스·공시 근거를 확인하지 못했습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="42" customHeight="1">
       <c r="A12" s="10" t="n">
         <v>2</v>
       </c>
@@ -1001,8 +1013,13 @@
           <t>Lumentum Holdings Inc.</t>
         </is>
       </c>
-    </row>
-    <row r="13" ht="28" customHeight="1">
+      <c r="L12" s="18" t="inlineStr">
+        <is>
+          <t>당일 뉴스·공시 근거를 확인하지 못했습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="42" customHeight="1">
       <c r="A13" s="10" t="n">
         <v>3</v>
       </c>
@@ -1052,8 +1069,13 @@
           <t>Teradyne, Inc.</t>
         </is>
       </c>
-    </row>
-    <row r="14" ht="28" customHeight="1">
+      <c r="L13" s="18" t="inlineStr">
+        <is>
+          <t>당일 뉴스·공시 근거를 확인하지 못했습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="42" customHeight="1">
       <c r="A14" s="10" t="n">
         <v>4</v>
       </c>
@@ -1103,8 +1125,13 @@
           <t>Axon Enterprise, Inc.</t>
         </is>
       </c>
-    </row>
-    <row r="15" ht="28" customHeight="1">
+      <c r="L14" s="18" t="inlineStr">
+        <is>
+          <t>당일 뉴스·공시 근거를 확인하지 못했습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="42" customHeight="1">
       <c r="A15" s="10" t="n">
         <v>5</v>
       </c>
@@ -1154,8 +1181,13 @@
           <t>Marvell Technology, Inc., together with its subsidiaries, provides data infrastructure semiconductor solutions and spanning the data center core to network edge in the United St...</t>
         </is>
       </c>
-    </row>
-    <row r="16" ht="28" customHeight="1">
+      <c r="L15" s="18" t="inlineStr">
+        <is>
+          <t>당일 뉴스·공시 근거를 확인하지 못했습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="42" customHeight="1">
       <c r="A16" s="10" t="n">
         <v>6</v>
       </c>
@@ -1205,8 +1237,13 @@
           <t>Brown-Forman Corporation, together with its subsidiaries, manufactures, distills, bottles, imports, exports, markets, and sells a variety of alcohol beverages.</t>
         </is>
       </c>
-    </row>
-    <row r="17" ht="28" customHeight="1">
+      <c r="L16" s="18" t="inlineStr">
+        <is>
+          <t>당일 뉴스·공시 근거를 확인하지 못했습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="42" customHeight="1">
       <c r="A17" s="10" t="n">
         <v>7</v>
       </c>
@@ -1256,8 +1293,13 @@
           <t>Coherent Corp.</t>
         </is>
       </c>
-    </row>
-    <row r="18" ht="28" customHeight="1">
+      <c r="L17" s="18" t="inlineStr">
+        <is>
+          <t>당일 뉴스·공시 근거를 확인하지 못했습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="42" customHeight="1">
       <c r="A18" s="10" t="n">
         <v>8</v>
       </c>
@@ -1307,8 +1349,13 @@
           <t>Sandisk Corporation develops, manufactures, and sells data storage devices and solutions using NAND flash technology in the United States, Europe, the Middle East, Africa, Asia,...</t>
         </is>
       </c>
-    </row>
-    <row r="19" ht="28" customHeight="1">
+      <c r="L18" s="18" t="inlineStr">
+        <is>
+          <t>당일 뉴스·공시 근거를 확인하지 못했습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="42" customHeight="1">
       <c r="A19" s="10" t="n">
         <v>9</v>
       </c>
@@ -1358,8 +1405,13 @@
           <t>DoorDash, Inc., together with its subsidiaries, operates a commerce platform that connects merchants, consumers, and dashers in the United States and internationally.</t>
         </is>
       </c>
-    </row>
-    <row r="20" ht="28" customHeight="1">
+      <c r="L19" s="18" t="inlineStr">
+        <is>
+          <t>당일 뉴스·공시 근거를 확인하지 못했습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="42" customHeight="1">
       <c r="A20" s="10" t="n">
         <v>10</v>
       </c>
@@ -1409,8 +1461,13 @@
           <t>LyondellBasell Industries N.V.</t>
         </is>
       </c>
-    </row>
-    <row r="21" ht="28" customHeight="1">
+      <c r="L20" s="18" t="inlineStr">
+        <is>
+          <t>당일 뉴스·공시 근거를 확인하지 못했습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="42" customHeight="1">
       <c r="A21" s="10" t="n">
         <v>11</v>
       </c>
@@ -1460,8 +1517,13 @@
           <t>Elevance Health, Inc., together with its subsidiaries, operates as a health benefits company in the United States.</t>
         </is>
       </c>
-    </row>
-    <row r="22" ht="28" customHeight="1">
+      <c r="L21" s="18" t="inlineStr">
+        <is>
+          <t>당일 뉴스·공시 근거를 확인하지 못했습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="42" customHeight="1">
       <c r="A22" s="10" t="n">
         <v>12</v>
       </c>
@@ -1511,8 +1573,13 @@
           <t>Akamai Technologies, Inc.</t>
         </is>
       </c>
-    </row>
-    <row r="23" ht="28" customHeight="1">
+      <c r="L22" s="18" t="inlineStr">
+        <is>
+          <t>당일 뉴스·공시 근거를 확인하지 못했습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="42" customHeight="1">
       <c r="A23" s="10" t="n">
         <v>13</v>
       </c>
@@ -1562,8 +1629,13 @@
           <t>Comfort Systems USA, Inc., together with its subsidiaries, provides mechanical and electrical installation, renovation, maintenance, repair, and replacement services for the mec...</t>
         </is>
       </c>
-    </row>
-    <row r="24" ht="28" customHeight="1">
+      <c r="L23" s="18" t="inlineStr">
+        <is>
+          <t>당일 뉴스·공시 근거를 확인하지 못했습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="42" customHeight="1">
       <c r="A24" s="10" t="n">
         <v>14</v>
       </c>
@@ -1613,8 +1685,13 @@
           <t>Intuitive Surgical, Inc.</t>
         </is>
       </c>
-    </row>
-    <row r="25" ht="28" customHeight="1">
+      <c r="L24" s="18" t="inlineStr">
+        <is>
+          <t>당일 뉴스·공시 근거를 확인하지 못했습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="42" customHeight="1">
       <c r="A25" s="10" t="n">
         <v>15</v>
       </c>
@@ -1664,8 +1741,13 @@
           <t>Microsoft Corporation develops and supports software, services, devices, and solutions worldwide.</t>
         </is>
       </c>
-    </row>
-    <row r="26" ht="28" customHeight="1">
+      <c r="L25" s="18" t="inlineStr">
+        <is>
+          <t>당일 뉴스·공시 근거를 확인하지 못했습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="42" customHeight="1">
       <c r="A26" s="10" t="n">
         <v>16</v>
       </c>
@@ -1715,8 +1797,13 @@
           <t>Western Digital Corporation develops, manufactures, and sells data storage devices and solutions based on hard disk drive (HDD) technology in the United States, Asia, Europe, th...</t>
         </is>
       </c>
-    </row>
-    <row r="27" ht="28" customHeight="1">
+      <c r="L26" s="18" t="inlineStr">
+        <is>
+          <t>당일 뉴스·공시 근거를 확인하지 못했습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="42" customHeight="1">
       <c r="A27" s="10" t="n">
         <v>17</v>
       </c>
@@ -1766,8 +1853,13 @@
           <t>Domino's Pizza, Inc.</t>
         </is>
       </c>
-    </row>
-    <row r="28" ht="28" customHeight="1">
+      <c r="L27" s="18" t="inlineStr">
+        <is>
+          <t>당일 뉴스·공시 근거를 확인하지 못했습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="42" customHeight="1">
       <c r="A28" s="10" t="n">
         <v>18</v>
       </c>
@@ -1817,8 +1909,13 @@
           <t>Transaction &amp; Payment Processing Services 분야의 미국 상장 기업</t>
         </is>
       </c>
-    </row>
-    <row r="29" ht="28" customHeight="1">
+      <c r="L28" s="18" t="inlineStr">
+        <is>
+          <t>당일 뉴스·공시 근거를 확인하지 못했습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="42" customHeight="1">
       <c r="A29" s="10" t="n">
         <v>19</v>
       </c>
@@ -1868,8 +1965,13 @@
           <t>The Progressive Corporation operates as an insurance company in the United States.</t>
         </is>
       </c>
-    </row>
-    <row r="30" ht="28" customHeight="1">
+      <c r="L29" s="18" t="inlineStr">
+        <is>
+          <t>당일 뉴스·공시 근거를 확인하지 못했습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="42" customHeight="1">
       <c r="A30" s="10" t="n">
         <v>20</v>
       </c>
@@ -1917,6 +2019,11 @@
       <c r="K30" s="18" t="inlineStr">
         <is>
           <t>Coinbase Global, Inc.</t>
+        </is>
+      </c>
+      <c r="L30" s="18" t="inlineStr">
+        <is>
+          <t>당일 뉴스·공시 근거를 확인하지 못했습니다.</t>
         </is>
       </c>
     </row>
@@ -1932,8 +2039,9 @@
       <c r="I31" s="20" t="n"/>
       <c r="J31" s="20" t="n"/>
       <c r="K31" s="20" t="n"/>
-    </row>
-    <row r="32" ht="28" customHeight="1">
+      <c r="L31" s="20" t="n"/>
+    </row>
+    <row r="32" ht="42" customHeight="1">
       <c r="A32" s="21" t="n">
         <v>503</v>
       </c>
@@ -1983,8 +2091,13 @@
           <t>Carvana Co., together with its subsidiaries, operates an e-commerce platform for buying and selling used cars.</t>
         </is>
       </c>
-    </row>
-    <row r="33" ht="28" customHeight="1">
+      <c r="L32" s="30" t="inlineStr">
+        <is>
+          <t>당일 뉴스·공시 근거를 확인하지 못했습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="42" customHeight="1">
       <c r="A33" s="21" t="n">
         <v>502</v>
       </c>
@@ -2034,8 +2147,13 @@
           <t>Honeywell Aerospace Inc.</t>
         </is>
       </c>
-    </row>
-    <row r="34" ht="28" customHeight="1">
+      <c r="L33" s="30" t="inlineStr">
+        <is>
+          <t>당일 뉴스·공시 근거를 확인하지 못했습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="42" customHeight="1">
       <c r="A34" s="21" t="n">
         <v>501</v>
       </c>
@@ -2085,8 +2203,13 @@
           <t>Oracle Corporation offers products and services that build, run and support enterprise information technology frameworks worldwide.</t>
         </is>
       </c>
-    </row>
-    <row r="35" ht="28" customHeight="1">
+      <c r="L34" s="30" t="inlineStr">
+        <is>
+          <t>당일 뉴스·공시 근거를 확인하지 못했습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="42" customHeight="1">
       <c r="A35" s="21" t="n">
         <v>499</v>
       </c>
@@ -2136,8 +2259,13 @@
           <t>KKR &amp; Co.</t>
         </is>
       </c>
-    </row>
-    <row r="36" ht="28" customHeight="1">
+      <c r="L35" s="30" t="inlineStr">
+        <is>
+          <t>당일 뉴스·공시 근거를 확인하지 못했습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="42" customHeight="1">
       <c r="A36" s="21" t="n">
         <v>500</v>
       </c>
@@ -2187,8 +2315,13 @@
           <t>United Parcel Service, Inc., a package delivery and logistics provider, offers transportation and delivery services.</t>
         </is>
       </c>
-    </row>
-    <row r="37" ht="28" customHeight="1">
+      <c r="L36" s="30" t="inlineStr">
+        <is>
+          <t>당일 뉴스·공시 근거를 확인하지 못했습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="42" customHeight="1">
       <c r="A37" s="21" t="n">
         <v>497</v>
       </c>
@@ -2238,8 +2371,13 @@
           <t>Warner Bros.</t>
         </is>
       </c>
-    </row>
-    <row r="38" ht="28" customHeight="1">
+      <c r="L37" s="30" t="inlineStr">
+        <is>
+          <t>당일 뉴스·공시 근거를 확인하지 못했습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="42" customHeight="1">
       <c r="A38" s="21" t="n">
         <v>498</v>
       </c>
@@ -2289,8 +2427,13 @@
           <t>Chipotle Mexican Grill, Inc., together with its subsidiaries, owns and operates Chipotle Mexican Grill restaurants.</t>
         </is>
       </c>
-    </row>
-    <row r="39" ht="28" customHeight="1">
+      <c r="L38" s="30" t="inlineStr">
+        <is>
+          <t>당일 뉴스·공시 근거를 확인하지 못했습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="42" customHeight="1">
       <c r="A39" s="21" t="n">
         <v>496</v>
       </c>
@@ -2340,8 +2483,13 @@
           <t>Moderna, Inc., a biotechnology company, provides messenger RNA medicines in the United States, Europe, and internationally.</t>
         </is>
       </c>
-    </row>
-    <row r="40" ht="28" customHeight="1">
+      <c r="L39" s="30" t="inlineStr">
+        <is>
+          <t>당일 뉴스·공시 근거를 확인하지 못했습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="42" customHeight="1">
       <c r="A40" s="21" t="n">
         <v>495</v>
       </c>
@@ -2391,8 +2539,13 @@
           <t>Dell Technologies Inc.</t>
         </is>
       </c>
-    </row>
-    <row r="41" ht="28" customHeight="1">
+      <c r="L40" s="30" t="inlineStr">
+        <is>
+          <t>당일 뉴스·공시 근거를 확인하지 못했습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="42" customHeight="1">
       <c r="A41" s="21" t="n">
         <v>493</v>
       </c>
@@ -2442,8 +2595,13 @@
           <t>Ares Management Corporation operates as an alternative asset manager.</t>
         </is>
       </c>
-    </row>
-    <row r="42" ht="28" customHeight="1">
+      <c r="L41" s="30" t="inlineStr">
+        <is>
+          <t>당일 뉴스·공시 근거를 확인하지 못했습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="42" customHeight="1">
       <c r="A42" s="21" t="n">
         <v>494</v>
       </c>
@@ -2493,8 +2651,13 @@
           <t>International Paper Company produces and sells renewable fiber-based packaging in North America, Latin America, Europe, South America, and North Africa.</t>
         </is>
       </c>
-    </row>
-    <row r="43" ht="28" customHeight="1">
+      <c r="L42" s="30" t="inlineStr">
+        <is>
+          <t>당일 뉴스·공시 근거를 확인하지 못했습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="42" customHeight="1">
       <c r="A43" s="21" t="n">
         <v>492</v>
       </c>
@@ -2544,8 +2707,13 @@
           <t>Revvity, Inc.</t>
         </is>
       </c>
-    </row>
-    <row r="44" ht="28" customHeight="1">
+      <c r="L43" s="30" t="inlineStr">
+        <is>
+          <t>당일 뉴스·공시 근거를 확인하지 못했습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="42" customHeight="1">
       <c r="A44" s="21" t="n">
         <v>491</v>
       </c>
@@ -2595,8 +2763,13 @@
           <t>First Solar, Inc., a solar technology company, provides photovoltaic (PV) solar energy solutions in the United States, France, India, Chile, and internationally.</t>
         </is>
       </c>
-    </row>
-    <row r="45" ht="28" customHeight="1">
+      <c r="L44" s="30" t="inlineStr">
+        <is>
+          <t>당일 뉴스·공시 근거를 확인하지 못했습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="42" customHeight="1">
       <c r="A45" s="21" t="n">
         <v>489</v>
       </c>
@@ -2646,8 +2819,13 @@
           <t>Waters Corporation provides analytical workflow solutions in Asia, the Americas, and Europe.</t>
         </is>
       </c>
-    </row>
-    <row r="46" ht="28" customHeight="1">
+      <c r="L45" s="30" t="inlineStr">
+        <is>
+          <t>당일 뉴스·공시 근거를 확인하지 못했습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="42" customHeight="1">
       <c r="A46" s="21" t="n">
         <v>490</v>
       </c>
@@ -2697,8 +2875,13 @@
           <t>D.R.</t>
         </is>
       </c>
-    </row>
-    <row r="47" ht="28" customHeight="1">
+      <c r="L46" s="30" t="inlineStr">
+        <is>
+          <t>당일 뉴스·공시 근거를 확인하지 못했습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="42" customHeight="1">
       <c r="A47" s="21" t="n">
         <v>488</v>
       </c>
@@ -2748,8 +2931,13 @@
           <t>United Rentals, Inc., through its subsidiaries, operates as an equipment rental company in the United States, Canada, Europe, Australia, and New Zealand.</t>
         </is>
       </c>
-    </row>
-    <row r="48" ht="28" customHeight="1">
+      <c r="L47" s="30" t="inlineStr">
+        <is>
+          <t>당일 뉴스·공시 근거를 확인하지 못했습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="42" customHeight="1">
       <c r="A48" s="21" t="n">
         <v>485</v>
       </c>
@@ -2799,8 +2987,13 @@
           <t>Stanley Black &amp; Decker, Inc.</t>
         </is>
       </c>
-    </row>
-    <row r="49" ht="28" customHeight="1">
+      <c r="L48" s="30" t="inlineStr">
+        <is>
+          <t>당일 뉴스·공시 근거를 확인하지 못했습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="42" customHeight="1">
       <c r="A49" s="21" t="n">
         <v>486</v>
       </c>
@@ -2850,8 +3043,13 @@
           <t>Tesla, Inc.</t>
         </is>
       </c>
-    </row>
-    <row r="50" ht="28" customHeight="1">
+      <c r="L49" s="30" t="inlineStr">
+        <is>
+          <t>당일 뉴스·공시 근거를 확인하지 못했습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="42" customHeight="1">
       <c r="A50" s="21" t="n">
         <v>487</v>
       </c>
@@ -2901,8 +3099,13 @@
           <t>Expeditors International of Washington, Inc., together with its subsidiaries, provides logistics services in the Americas, North Asia, South Asia, Europe, and Middle East, Afric...</t>
         </is>
       </c>
-    </row>
-    <row r="51" ht="28" customHeight="1">
+      <c r="L50" s="30" t="inlineStr">
+        <is>
+          <t>당일 뉴스·공시 근거를 확인하지 못했습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="42" customHeight="1">
       <c r="A51" s="21" t="n">
         <v>484</v>
       </c>
@@ -2952,6 +3155,11 @@
           <t>CRH plc, together with its subsidiaries, provides building materials solutions in Ireland, the United States, the United Kingdom, rest of Europe, and internationally.</t>
         </is>
       </c>
+      <c r="L51" s="30" t="inlineStr">
+        <is>
+          <t>당일 뉴스·공시 근거를 확인하지 못했습니다.</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="31" t="inlineStr">
@@ -2965,25 +3173,26 @@
         <is>
           <t>관측: 상승 157개·하락 326개로 상승 비율은 33%였습니다. 강세 섹터는 Communication Services +1.0%, Energy +0.6%, 약세 섹터는 Health Care -1.2%, Materials -0.9%였습니다. 개별 종목 중 GPN(+5.8%)가 가장 강했고, CVNA(-4.8%)가 가장 약했습니다.
 해석: 시장 폭이 약해 단기적으로 방어적 포지셔닝과 변동성 확대 가능성에 유의할 구간입니다.
-유의: 본 요약은 가격·시장 폭·섹터 수익률에 근거한 관측이며, 뉴스·실적 등 원인을 직접 분석한 투자 의견은 아닙니다.</t>
+유의: AI 요약은 제공된 Yahoo Finance 기업 설명·뉴스 헤드라인과 시장 데이터만 근거로 하며 투자 의견이 아닙니다.</t>
         </is>
       </c>
     </row>
     <row r="56"/>
     <row r="57"/>
   </sheetData>
-  <mergeCells count="13">
+  <mergeCells count="14">
     <mergeCell ref="C9:C10"/>
     <mergeCell ref="B9:B10"/>
+    <mergeCell ref="A54:L54"/>
     <mergeCell ref="D9:D10"/>
     <mergeCell ref="E9:H9"/>
     <mergeCell ref="I9:I10"/>
+    <mergeCell ref="A55:L57"/>
     <mergeCell ref="G7:H7"/>
     <mergeCell ref="A9:A10"/>
     <mergeCell ref="J9:J10"/>
     <mergeCell ref="K9:K10"/>
-    <mergeCell ref="A54:K54"/>
-    <mergeCell ref="A55:K57"/>
+    <mergeCell ref="L9:L10"/>
     <mergeCell ref="G2:J5"/>
     <mergeCell ref="G6:H6"/>
   </mergeCells>
